--- a/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 0,18</t>
+          <t>-23,89; 0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 8,79</t>
+          <t>-3,25; 8,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 4,78</t>
+          <t>-16,92; 4,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 16,51</t>
+          <t>-6,31; 17,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 9,73</t>
+          <t>-8,35; 9,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 4,06</t>
+          <t>-18,3; 3,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 4,68</t>
+          <t>-16,75; 5,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 281,05</t>
+          <t>-47,07; 350,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 228,94</t>
+          <t>-69,53; 238,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-93,36; 109,79</t>
+          <t>-100,0; 88,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,93; 96,81</t>
+          <t>-89,97; 92,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 24,1</t>
+          <t>-16,42; 23,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 7,24</t>
+          <t>-29,9; 10,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 21,61</t>
+          <t>-11,03; 20,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 17,39</t>
+          <t>-8,49; 17,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 213,42</t>
+          <t>-58,41; 185,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,55; 49,62</t>
+          <t>-74,2; 73,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 183,46</t>
+          <t>-44,54; 197,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,85; 354,17</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 14,19</t>
+          <t>-17,8; 13,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 19,15</t>
+          <t>-21,44; 18,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 24,93</t>
+          <t>-17,76; 25,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 6,08</t>
+          <t>-16,78; 6,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 89,33</t>
+          <t>-60,64; 90,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 148,02</t>
+          <t>-61,54; 140,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 258,62</t>
+          <t>-62,37; 310,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,91; 81,93</t>
+          <t>-86,59; 94,43</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 7,03</t>
+          <t>-7,48; 6,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 5,91</t>
+          <t>-6,68; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,46</t>
+          <t>-8,45; 7,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,64</t>
+          <t>-8,19; 3,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 55,85</t>
+          <t>-38,72; 53,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 62,87</t>
+          <t>-42,51; 62,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 55,84</t>
+          <t>-43,91; 70,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 50,59</t>
+          <t>-62,8; 52,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 0,25</t>
+          <t>-22,62; 0,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 8,48</t>
+          <t>-3,31; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 4,51</t>
+          <t>-16,77; 4,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 17,82</t>
+          <t>-6,26; 18,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 9,58</t>
+          <t>-7,13; 10,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 3,3</t>
+          <t>-18,89; 3,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 5,26</t>
+          <t>-17,05; 4,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 350,16</t>
+          <t>-47,79; 320,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,53; 238,14</t>
+          <t>-65,46; 263,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,54</t>
+          <t>-92,38; 102,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,97; 92,18</t>
+          <t>-86,65; 96,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 23,52</t>
+          <t>-17,2; 25,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 10,6</t>
+          <t>-28,64; 8,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 20,22</t>
+          <t>-10,96; 20,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 17,81</t>
+          <t>-7,71; 18,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 185,01</t>
+          <t>-56,19; 204,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 73,38</t>
+          <t>-75,46; 46,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 197,53</t>
+          <t>-41,32; 208,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 354,17</t>
+          <t>-56,32; 353,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 13,25</t>
+          <t>-19,49; 16,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 18,93</t>
+          <t>-21,5; 18,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 25,61</t>
+          <t>-14,43; 26,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 6,27</t>
+          <t>-15,44; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 90,12</t>
+          <t>-63,4; 103,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,54; 140,92</t>
+          <t>-64,79; 131,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 310,63</t>
+          <t>-52,63; 297,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,59; 94,43</t>
+          <t>-85,51; 80,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,89</t>
+          <t>-7,32; 7,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,09</t>
+          <t>-6,75; 5,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,19</t>
+          <t>-8,06; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,95</t>
+          <t>-7,72; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 53,68</t>
+          <t>-38,46; 55,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 62,47</t>
+          <t>-42,07; 60,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 70,67</t>
+          <t>-44,31; 55,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 52,54</t>
+          <t>-58,5; 51,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 0,02</t>
+          <t>-22,07; 0,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,25</t>
+          <t>-3,28; 8,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 4,51</t>
+          <t>-17,04; 4,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,95</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-39,16%</t>
+          <t>-20,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 18,53</t>
+          <t>-6,55; 16,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 10,16</t>
+          <t>-7,77; 9,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 3,27</t>
+          <t>-17,08; 4,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 4,98</t>
+          <t>-12,9; 7,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 320,13</t>
+          <t>-48,58; 281,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 263,15</t>
+          <t>-70,32; 228,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,38; 102,59</t>
+          <t>-93,36; 109,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 96,6</t>
+          <t>-82,17; 142,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 25,0</t>
+          <t>-16,2; 24,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 8,12</t>
+          <t>-29,2; 7,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 20,96</t>
+          <t>-10,69; 21,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 18,02</t>
+          <t>-7,67; 17,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 204,01</t>
+          <t>-55,33; 213,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 46,73</t>
+          <t>-77,55; 49,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 208,43</t>
+          <t>-44,95; 183,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,32; 353,03</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,84%</t>
+          <t>-1,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 16,08</t>
+          <t>-17,79; 14,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 18,71</t>
+          <t>-20,86; 19,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 26,18</t>
+          <t>-18,24; 24,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 5,92</t>
+          <t>-12,27; 11,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 103,37</t>
+          <t>-62,22; 89,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,79; 131,76</t>
+          <t>-62,96; 148,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 297,95</t>
+          <t>-66,2; 258,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,51; 80,41</t>
+          <t>-67,1; 192,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,08</t>
+          <t>-7,67; 7,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,7</t>
+          <t>-6,53; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,69</t>
+          <t>-8,12; 6,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,87</t>
+          <t>-6,03; 6,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 55,48</t>
+          <t>-37,86; 55,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 60,27</t>
+          <t>-42,57; 62,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 55,02</t>
+          <t>-46,22; 55,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 51,23</t>
+          <t>-46,01; 89,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-9,83</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-80,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>108,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-47,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-2.330793842344286</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4186723972663865</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7170846539580854</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.7768501358307605</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.9728898287377175</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.4456329915645244</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-22,07; 0,18</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 8,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-17,04; 4,78</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.654418204731821</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.53143734461546</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.300922206650764</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1401031589809772</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.085308767776051</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.079788872105706</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,58</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,67</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-53,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-20,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 16,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,77; 9,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-17,08; 4,06</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,9; 7,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-48,58; 281,05</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-70,32; 228,94</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-93,36; 109,79</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-82,17; 142,39</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4507634710285261</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.002245584818831234</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.9221663768266509</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4302671879394433</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2040874670448371</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.001105691213525758</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.4465937275388001</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1473388343464906</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-9,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-34,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.688746208433102</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.00676821486623</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.776743176850808</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.995555081953511</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5441073551875107</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6888976757522307</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.789424471495366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-16,2; 24,1</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-29,2; 7,24</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,69; 21,61</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,67; 17,86</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,33; 213,42</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-77,55; 49,62</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-44,95; 183,46</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.022683110030288</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.337963337771438</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.006146264468898</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.916705292060584</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.861245613130634</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.810925543539602</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.418685902771048</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.302462093458812</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +797,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-5,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-1,92%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.7728364867317421</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.50819962158335</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.256853057419943</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.9440053025231216</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2116949169156504</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2996617420044287</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3733367586946962</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3928105106404978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,79; 14,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-20,86; 19,15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-18,24; 24,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-12,27; 11,72</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-62,22; 89,33</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-62,96; 148,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-66,2; 258,62</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-67,1; 192,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.129944301239429</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.548369606308307</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.177384928115065</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.917974287729146</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6041982134300957</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7793277758895406</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4791223380983508</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.620794590597218</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.023633561694376</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.801843203833156</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.654406540645772</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.240568298822376</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.445104457371453</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7094433049857322</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.637212930736328</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.869552106897947</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.131975261646395</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2538264695381542</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4208751070444685</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.2697342885752491</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2592169865739817</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.07552634784857643</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1592465297711584</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1026315471735937</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.591778955248449</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.040762941027632</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.416827511055383</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.893190713717779</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7271484858330064</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6312019121088676</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6420862845175966</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7334153460094215</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.959409675579267</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.632722346013129</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.411394936411456</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.192792297905606</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7450843651629703</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.234551876488657</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.621440358423164</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.405187620396678</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-6,73%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,67; 7,03</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,53; 5,91</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,12; 6,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 6,56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-37,86; 55,85</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-42,57; 62,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-46,22; 55,84</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-46,01; 89,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.395708881312417</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1697209045577849</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04844959860439597</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.02731939975422308</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1221573719578321</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.06362321552146143</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01974695493197374</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.01119811055061635</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.816572512265673</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.567397481053771</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.457243137778523</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.559840166163025</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4719669554203281</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4701069592103087</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4452118627030113</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.487800810091196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.260808955026806</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.240097342562043</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.545906819941361</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.609333746894324</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.511812201717574</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.6891210814525509</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.878297629535423</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9580522599839997</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1095,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
